--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513858_FF2ºB32ºB42ºB32ºB4_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513858_FF2ºB32ºB42ºB32ºB4_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4543</v>
+        <v>5.3616</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3807</v>
+        <v>3.8274</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0736</v>
+        <v>1.5342</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0385</v>
+        <v>4.1487</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08</v>
+        <v>2.1922</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9585</v>
+        <v>1.9566</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4568</v>
+        <v>3.6657</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0931</v>
+        <v>2.3605</v>
       </c>
       <c r="L2" t="n">
-        <v>3.3637</v>
+        <v>1.3052</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5817</v>
+        <v>0.483</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0131</v>
+        <v>-0.1684</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5948</v>
+        <v>0.6514</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5842000000000001</v>
+        <v>1.5579</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.1158</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5316</v>
+        <v>1.5579</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>-0.2935</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0397</v>
+        <v>0.2132</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0397</v>
+        <v>-0.5067</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-0.0516</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-0.0516</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4071</v>
+        <v>5.2033</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2402</v>
+        <v>2.4079</v>
       </c>
       <c r="F3" t="n">
-        <v>0.167</v>
+        <v>2.7953</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9469</v>
+        <v>5.0385</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.335</v>
+        <v>0.08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2819</v>
+        <v>4.9585</v>
       </c>
       <c r="J3" t="n">
-        <v>2.402</v>
+        <v>4.4568</v>
       </c>
       <c r="K3" t="n">
-        <v>1.632</v>
+        <v>1.0931</v>
       </c>
       <c r="L3" t="n">
-        <v>0.77</v>
+        <v>3.3637</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4551</v>
+        <v>0.5817</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.967</v>
+        <v>-1.0131</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5119</v>
+        <v>1.5948</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1947</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9737</v>
+        <v>-3.1158</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1684</v>
+        <v>2.5316</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5439</v>
+        <v>0.7489</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8108</v>
+        <v>1.0669</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7331</v>
+        <v>-0.318</v>
       </c>
       <c r="V3" t="n">
-        <v>2.7216</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.0011</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2532</v>
+        <v>4.7898</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7362</v>
+        <v>5.0681</v>
       </c>
       <c r="F4" t="n">
-        <v>1.517</v>
+        <v>-0.2782</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5356</v>
+        <v>0.9469</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6214</v>
+        <v>-0.335</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9143</v>
+        <v>1.2819</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3026</v>
+        <v>2.402</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4516</v>
+        <v>1.632</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8511</v>
+        <v>0.77</v>
       </c>
       <c r="M4" t="n">
-        <v>1.233</v>
+        <v>-1.4551</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1698</v>
+        <v>-1.967</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0632</v>
+        <v>0.5119</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5579</v>
+        <v>0.1947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1947</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7526</v>
+        <v>1.1684</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9397</v>
+        <v>0.9266</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3489</v>
+        <v>0.6387</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5908</v>
+        <v>0.2879</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.78</v>
+        <v>2.7216</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2795</v>
+        <v>3.0011</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.0595</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5053</v>
+        <v>3.6181</v>
       </c>
       <c r="E5" t="n">
-        <v>3.305</v>
+        <v>2.6019</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2003</v>
+        <v>1.0161</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1487</v>
+        <v>2.5356</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1922</v>
+        <v>0.6214</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9566</v>
+        <v>1.9143</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6657</v>
+        <v>1.3026</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3605</v>
+        <v>0.4516</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3052</v>
+        <v>0.8511</v>
       </c>
       <c r="M5" t="n">
-        <v>0.483</v>
+        <v>1.233</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1684</v>
+        <v>0.1698</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6514</v>
+        <v>1.0632</v>
       </c>
       <c r="P5" t="n">
         <v>1.5579</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5579</v>
+        <v>1.7526</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1498</v>
+        <v>1.3045</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3092</v>
+        <v>1.2146</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8406</v>
+        <v>0.09</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0516</v>
+        <v>-1.78</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0516</v>
+        <v>0.2795</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.0595</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0791</v>
+        <v>3.4276</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5238</v>
+        <v>0.4351</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6029</v>
+        <v>2.9925</v>
       </c>
       <c r="G6" t="n">
         <v>4.2788</v>
@@ -922,13 +922,13 @@
         <v>2.3368</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4929</v>
+        <v>-0.1444</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9275</v>
+        <v>0.0314</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5654</v>
+        <v>-0.1758</v>
       </c>
       <c r="V6" t="n">
         <v>2.2142</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8368</v>
+        <v>2.4805</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0361</v>
+        <v>2.3181</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1993</v>
+        <v>0.1624</v>
       </c>
       <c r="G7" t="n">
         <v>2.4515</v>
@@ -1000,13 +1000,13 @@
         <v>1.5579</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1931</v>
+        <v>0.4506</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7854</v>
+        <v>0.4965</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4077</v>
+        <v>-0.0459</v>
       </c>
       <c r="V7" t="n">
         <v>0.9416</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. VAN BRANDWIJK</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4698</v>
+        <v>0.604</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4698</v>
+        <v>-2.0088</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2.6128</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2.4101</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-1.4852</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3.8953</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.2599</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.1103</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.3702</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.1502</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-1.3749</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.5251</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1947</v>
+        <v>-3.1158</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1947</v>
+        <v>-5.0631</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.9474</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6645</v>
+        <v>0.4197</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6645</v>
+        <v>0.9045</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.4848</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MONTENEGRO MOYA</t>
+          <t>K. VAN BRANDWIJK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1947</v>
+        <v>0.0711</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1947</v>
+        <v>0.0711</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.2658</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.2658</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>A. MONTENEGRO MOYA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2361</v>
+        <v>-0.0951</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4315</v>
+        <v>-0.0951</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1954</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4101</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4852</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8953</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2599</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1103</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3702</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1502</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3749</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5251</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.1158</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.0631</v>
+        <v>-0.1947</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9474</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4204</v>
+        <v>0.0997</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4818</v>
+        <v>0.0997</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9022</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. PANOS HUERTAS</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8292</v>
+        <v>-1.2796</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9006</v>
+        <v>-0.4636</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9287</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1847</v>
+        <v>-2.9607</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4505</v>
+        <v>-1.0566</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2658</v>
+        <v>-1.9041</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.644</v>
+        <v>-0.9371</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.644</v>
+        <v>0.4157</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.3528</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4592</v>
+        <v>-2.0236</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1934</v>
+        <v>-1.4723</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2658</v>
+        <v>-0.5513</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1947</v>
+        <v>-1.1684</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1947</v>
+        <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4234</v>
+        <v>0.7395</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0618</v>
+        <v>0.4209</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3616</v>
+        <v>0.3186</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2211</v>
+        <v>0.9416</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2211</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>L. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3777</v>
+        <v>-1.6739</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4225</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9552</v>
+        <v>-0.873</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9607</v>
+        <v>-0.1847</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0566</v>
+        <v>-0.4505</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9041</v>
+        <v>0.2658</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9371</v>
+        <v>-0.644</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4157</v>
+        <v>-0.644</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3528</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.0236</v>
+        <v>0.4592</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4723</v>
+        <v>0.1934</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5513</v>
+        <v>0.2658</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1684</v>
+        <v>-0.1947</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1684</v>
+        <v>0.1947</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3586</v>
+        <v>-0.2681</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5381</v>
+        <v>0.0378</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1795</v>
+        <v>-0.306</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9416</v>
+        <v>-1.2211</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2795</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5469</v>
+        <v>-2.7587</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0027</v>
+        <v>-1.7415</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5442</v>
+        <v>-1.0173</v>
       </c>
       <c r="G13" t="n">
         <v>-1.5461</v>
@@ -1468,13 +1468,13 @@
         <v>0.3895</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3108</v>
+        <v>1.099</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1265</v>
+        <v>0.3876</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1844</v>
+        <v>0.7113</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5590000000000001</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.821</v>
+        <v>19.7487</v>
       </c>
       <c r="E14" t="n">
-        <v>10.6922</v>
+        <v>11.6197</v>
       </c>
       <c r="F14" t="n">
         <v>8.1288</v>
@@ -1513,7 +1513,7 @@
         <v>17.1186</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2437000000000009</v>
+        <v>0.2437</v>
       </c>
       <c r="I14" t="n">
         <v>16.8751</v>
@@ -1534,7 +1534,7 @@
         <v>-9.348000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>7.8755</v>
+        <v>7.875499999999999</v>
       </c>
       <c r="P14" t="n">
         <v>-6.815700000000001</v>
@@ -1546,13 +1546,13 @@
         <v>14.6052</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4207</v>
+        <v>5.3483</v>
       </c>
       <c r="T14" t="n">
-        <v>4.8502</v>
+        <v>5.7776</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4294000000000002</v>
+        <v>-0.4294</v>
       </c>
       <c r="V14" t="n">
         <v>4.0973</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1877</v>
+        <v>0.789</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8087</v>
+        <v>0.41</v>
       </c>
       <c r="F15" t="n">
         <v>0.3789</v>
@@ -1624,10 +1624,10 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4079</v>
+        <v>0.0092</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.1421</v>
       </c>
       <c r="U15" t="n">
         <v>-0.1329</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3359</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8423</v>
+        <v>1.2811</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5063</v>
+        <v>-1.2718</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.4782</v>
+        <v>-0.9094</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3002</v>
+        <v>0.6937</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7784</v>
+        <v>-1.6032</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3994</v>
+        <v>1.4536</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2778</v>
+        <v>2.0937</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1216</v>
+        <v>-0.6401</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8776</v>
+        <v>-2.3631</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9776</v>
+        <v>-1.4</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9</v>
+        <v>-0.9631</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9737</v>
+        <v>1.3632</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9737</v>
+        <v>-1.1684</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9474</v>
+        <v>2.5316</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8404</v>
+        <v>-0.4444</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1371</v>
+        <v>-0.2252</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2966</v>
+        <v>-0.2192</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2795</v>
+        <v>1.2211</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2795</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2125</v>
+        <v>-0.0448</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6502</v>
+        <v>2.7798</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4377</v>
+        <v>-2.8246</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4115</v>
+        <v>3.3167</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3089</v>
+        <v>3.8471</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1026</v>
+        <v>-0.5304</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8134</v>
+        <v>4.0073</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8134</v>
+        <v>3.9668</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2249</v>
+        <v>-0.6906</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1223</v>
+        <v>-0.1197</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1026</v>
+        <v>-0.571</v>
       </c>
       <c r="P17" t="n">
+        <v>0.7789</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.9737</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.7526</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-0.1947</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.9474</v>
-      </c>
       <c r="S17" t="n">
-        <v>-0.4081</v>
+        <v>-0.4257</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4726</v>
+        <v>-0.4817</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8807</v>
+        <v>0.056</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2795</v>
+        <v>-3.7147</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.2279</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2795</v>
+        <v>-3.9426</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>H. MARTORELL TRONCHONI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2484</v>
+        <v>-0.2338</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9227</v>
+        <v>-0.792</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6743</v>
+        <v>0.5582</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0992</v>
+        <v>-0.9401</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.504</v>
+        <v>-0.2755</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6032</v>
+        <v>-0.6645</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1056</v>
+        <v>-1.0006</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1185</v>
+        <v>-0.3361</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2241</v>
+        <v>-0.6645</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0064</v>
+        <v>0.0605</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3855</v>
+        <v>0.0605</v>
       </c>
       <c r="O18" t="n">
-        <v>0.379</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7789</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7526</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.516</v>
+        <v>0.1221</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7236</v>
+        <v>0.2086</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2075</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3311</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3221</v>
+        <v>-0.2419</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7827</v>
+        <v>1.2515</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1048</v>
+        <v>-1.4933</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9094</v>
+        <v>-1.4115</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6937</v>
+        <v>-0.3089</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6032</v>
+        <v>-1.1026</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4536</v>
+        <v>0.8134</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0937</v>
+        <v>0.8134</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6401</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3631</v>
+        <v>-2.2249</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4</v>
+        <v>-1.1223</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9631</v>
+        <v>-1.1026</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3632</v>
+        <v>1.7526</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1684</v>
+        <v>-0.1947</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5316</v>
+        <v>1.9474</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7758</v>
+        <v>-0.8625</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7236</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0523</v>
+        <v>-0.9363</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2211</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2211</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4472</v>
+        <v>-0.2555</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2814</v>
+        <v>-1.6237</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7287</v>
+        <v>1.3682</v>
       </c>
       <c r="G20" t="n">
-        <v>3.3167</v>
+        <v>0.0992</v>
       </c>
       <c r="H20" t="n">
-        <v>3.8471</v>
+        <v>-1.504</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5304</v>
+        <v>1.6032</v>
       </c>
       <c r="J20" t="n">
-        <v>4.0073</v>
+        <v>0.1056</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9668</v>
+        <v>-1.1185</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0405</v>
+        <v>1.2241</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6906</v>
+        <v>-0.0064</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1197</v>
+        <v>-0.3855</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.571</v>
+        <v>0.379</v>
       </c>
       <c r="P20" t="n">
         <v>0.7789</v>
@@ -2014,28 +2014,28 @@
         <v>1.7526</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.5231</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9801</v>
+        <v>-0.4245</v>
       </c>
       <c r="U20" t="n">
-        <v>0.152</v>
+        <v>-0.0985</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.7147</v>
+        <v>-0.6105</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2279</v>
+        <v>-0.3311</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.9426</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. MARTORELL TRONCHONI</t>
+          <t>R. MALLIK BOUNAD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.461</v>
+        <v>-0.2945</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9913999999999999</v>
+        <v>1.0449</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5304</v>
+        <v>-1.3394</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9401</v>
+        <v>-1.4782</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2755</v>
+        <v>0.3002</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6645</v>
+        <v>-1.7784</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0006</v>
+        <v>1.3994</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3361</v>
+        <v>1.2778</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6645</v>
+        <v>0.1216</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0605</v>
+        <v>-2.8776</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0605</v>
+        <v>-0.9776</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-1.9</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.9474</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1051</v>
+        <v>0.21</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0092</v>
+        <v>0.3397</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1144</v>
+        <v>-0.1297</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2554</v>
+        <v>-2.216</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2245</v>
+        <v>-1.3242</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0309</v>
+        <v>-0.8918</v>
       </c>
       <c r="G22" t="n">
         <v>-3.6153</v>
@@ -2170,13 +2170,13 @@
         <v>1.5579</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0032</v>
+        <v>0.0362</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2409</v>
+        <v>0.1412</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2441</v>
+        <v>-0.105</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6446</v>
+        <v>-2.3453</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2117</v>
+        <v>-1.9088</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4329</v>
+        <v>-0.4365</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2914</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6353</v>
+        <v>2.5421</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3439</v>
+        <v>-3.4882</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4281</v>
+        <v>0.6314</v>
       </c>
       <c r="K23" t="n">
-        <v>1.3471</v>
+        <v>3.9539</v>
       </c>
       <c r="L23" t="n">
-        <v>0.08110000000000001</v>
+        <v>-3.3225</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1367</v>
+        <v>-1.5775</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7118</v>
+        <v>-1.4118</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4249</v>
+        <v>-0.1657</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3632</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.921</v>
+        <v>-3.1158</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5579</v>
+        <v>2.3368</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9209000000000001</v>
+        <v>-1.1793</v>
       </c>
       <c r="T23" t="n">
-        <v>1.3844</v>
+        <v>0.0166</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4635</v>
+        <v>-1.1959</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4937</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.1032</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.3905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5221</v>
+        <v>-3.1529</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1903</v>
+        <v>-1.2084</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6682</v>
+        <v>-1.9445</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.6812</v>
+        <v>0.2914</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6322</v>
+        <v>0.6353</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.049</v>
+        <v>-0.3439</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.5129</v>
+        <v>1.4281</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1743</v>
+        <v>1.3471</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.3386</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1682</v>
+        <v>-1.1367</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4578</v>
+        <v>-0.7118</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7104</v>
+        <v>-0.4249</v>
       </c>
       <c r="P24" t="n">
-        <v>1.3632</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9737</v>
+        <v>-2.921</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3368</v>
+        <v>1.5579</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2041</v>
+        <v>0.4126</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2963</v>
+        <v>0.3876</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5003</v>
+        <v>0.0249</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-2.4937</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.1032</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-2.3905</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.747</v>
+        <v>-3.4835</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9056</v>
+        <v>-4.3897</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8415</v>
+        <v>0.9062</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-4.6812</v>
       </c>
       <c r="H25" t="n">
-        <v>2.5421</v>
+        <v>-0.6322</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.4882</v>
+        <v>-4.049</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6314</v>
+        <v>-3.5129</v>
       </c>
       <c r="K25" t="n">
-        <v>3.9539</v>
+        <v>-0.1743</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.3225</v>
+        <v>-3.3386</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5775</v>
+        <v>-1.1682</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4118</v>
+        <v>-0.4578</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1657</v>
+        <v>-0.7104</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.7789</v>
+        <v>1.3632</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.1158</v>
+        <v>-0.9737</v>
       </c>
       <c r="R25" t="n">
         <v>2.3368</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.581</v>
+        <v>-0.1654</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9801</v>
+        <v>0.0969</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.6008</v>
+        <v>-0.2624</v>
       </c>
       <c r="V25" t="n">
-        <v>0.5590000000000001</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5590000000000001</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.9093</v>
+        <v>-6.0222</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.9895</v>
+        <v>-4.5908</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.9197</v>
+        <v>-1.4313</v>
       </c>
       <c r="G26" t="n">
         <v>-6.7923</v>
@@ -2482,13 +2482,13 @@
         <v>2.5316</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1686</v>
+        <v>-0.2815</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2446</v>
+        <v>0.1541</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.924</v>
+        <v>-0.4356</v>
       </c>
       <c r="V26" t="n">
         <v>0.6621</v>
@@ -2515,28 +2515,28 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-18.821</v>
+        <v>-17.4921</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.070399999999999</v>
+        <v>-9.0703</v>
       </c>
       <c r="F27" t="n">
-        <v>-9.7507</v>
+        <v>-8.4217</v>
       </c>
       <c r="G27" t="n">
         <v>-17.1186</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2435999999999998</v>
+        <v>-0.2436000000000003</v>
       </c>
       <c r="I27" t="n">
         <v>-16.8749</v>
       </c>
       <c r="J27" t="n">
-        <v>1.472199999999999</v>
+        <v>1.4722</v>
       </c>
       <c r="K27" t="n">
-        <v>9.348000000000001</v>
+        <v>9.347999999999999</v>
       </c>
       <c r="L27" t="n">
         <v>-7.8757</v>
@@ -2560,16 +2560,16 @@
         <v>21.421</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.4208</v>
+        <v>-3.0918</v>
       </c>
       <c r="T27" t="n">
         <v>0.4292999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.8501</v>
+        <v>-3.5211</v>
       </c>
       <c r="V27" t="n">
-        <v>-4.097200000000001</v>
+        <v>-4.0972</v>
       </c>
       <c r="W27" t="n">
         <v>3.6333</v>
